--- a/docs/oc-mensuales/suministro-de-combustibles/jun-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/jun-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>27673.72</v>
+        <v>28069.7</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6088.22</v>
+        <v>6175.33</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>27740.35</v>
+        <v>28137.29</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>26903.83</v>
+        <v>27288.8</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4919.17</v>
+        <v>4989.56</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>14390.33</v>
+        <v>14596.25</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>14292.37</v>
+        <v>14496.88</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5534.74</v>
+        <v>5613.94</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11069.49</v>
+        <v>11227.88</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6088.22</v>
+        <v>6175.33</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4771.47</v>
+        <v>4839.75</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4333.82</v>
+        <v>4395.83</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11069.49</v>
+        <v>11227.88</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2435.29</v>
+        <v>2470.13</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10432.82</v>
+        <v>10582.1</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9409.059999999999</v>
+        <v>9543.700000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4427.79</v>
+        <v>4491.15</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6862.78</v>
+        <v>6960.99</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4206.4</v>
+        <v>4266.59</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>24352.87</v>
+        <v>24701.34</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3320.85</v>
+        <v>3368.36</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3320.85</v>
+        <v>3368.36</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6641.69</v>
+        <v>6736.73</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>16604.23</v>
+        <v>16841.82</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>33208.46</v>
+        <v>33683.64</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7748.64</v>
+        <v>7859.52</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>18818.13</v>
+        <v>19087.4</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>8855.59</v>
+        <v>8982.299999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2767.37</v>
+        <v>2806.97</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5534.74</v>
+        <v>5613.94</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>22138.97</v>
+        <v>22455.76</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3320.85</v>
+        <v>3368.36</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2988.76</v>
+        <v>3031.53</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>13283.38</v>
+        <v>13473.46</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>71951.66</v>
+        <v>72981.23</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4197.55</v>
+        <v>4257.61</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3320.85</v>
+        <v>3368.36</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4427.79</v>
+        <v>4491.15</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4427.79</v>
+        <v>4491.15</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2435.29</v>
+        <v>2470.13</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5534.74</v>
+        <v>5613.94</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3320.85</v>
+        <v>3368.36</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5534.74</v>
+        <v>5599.67</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2767.37</v>
+        <v>2799.83</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4427.79</v>
+        <v>4479.73</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4514.74</v>
+        <v>4567.7</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>22138.97</v>
+        <v>22398.67</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>17711.18</v>
+        <v>17918.94</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3874.32</v>
+        <v>3919.77</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2948.91</v>
+        <v>2983.5</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>20098.1</v>
+        <v>20333.86</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>17711.18</v>
+        <v>17918.94</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>11069.49</v>
+        <v>11199.34</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>7748.64</v>
+        <v>7839.54</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8855.59</v>
+        <v>8959.469999999999</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>5534.74</v>
+        <v>5599.67</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>6641.69</v>
+        <v>6719.6</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>4283.89</v>
+        <v>4334.14</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>17711.18</v>
+        <v>17918.94</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3320.85</v>
+        <v>3359.8</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2379.94</v>
+        <v>2407.86</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>23799.4</v>
+        <v>24078.57</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4427.79</v>
+        <v>4479.73</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>11069.49</v>
+        <v>11199.34</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>7029.12</v>
+        <v>7111.58</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>11069.49</v>
+        <v>11199.34</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>5534.74</v>
+        <v>5599.67</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>27673.72</v>
+        <v>27998.34</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3320.85</v>
+        <v>3359.8</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>6641.69</v>
+        <v>6719.6</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3462.02</v>
+        <v>3502.63</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>3320.85</v>
+        <v>3359.8</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2435.29</v>
+        <v>2463.85</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>37636.25</v>
+        <v>38077.75</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3874.32</v>
+        <v>3919.77</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2379.94</v>
+        <v>2407.86</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>11855.42</v>
+        <v>11994.49</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4427.79</v>
+        <v>4479.73</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2435.29</v>
+        <v>2463.85</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>16604.23</v>
+        <v>16799.01</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>36772.83</v>
+        <v>37204.2</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2374.6</v>
+        <v>2402.46</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>14667.07</v>
+        <v>14915.12</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>23113.09</v>
+        <v>23503.98</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4427.79</v>
+        <v>4502.68</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>8855.59</v>
+        <v>9005.360000000001</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2435.29</v>
+        <v>2476.47</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>4968.73</v>
+        <v>5052.77</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>4427.79</v>
+        <v>4502.68</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>10958.79</v>
+        <v>11144.13</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>13283.38</v>
+        <v>13508.04</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>11069.49</v>
+        <v>11256.7</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>16604.23</v>
+        <v>16885.05</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>6641.69</v>
+        <v>6754.02</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>34468.32</v>
+        <v>35051.26</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>11069.49</v>
+        <v>11256.7</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>6641.69</v>
+        <v>6754.02</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>12176.43</v>
+        <v>12382.37</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>5534.74</v>
+        <v>5628.35</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2767.37</v>
+        <v>2814.17</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>6641.69</v>
+        <v>6754.02</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2435.29</v>
+        <v>2476.47</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2379.94</v>
+        <v>2420.19</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>9962.540000000001</v>
+        <v>10131.03</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>37629.69</v>
+        <v>38266.1</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>28780.66</v>
+        <v>29267.41</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>10538.15</v>
+        <v>10716.38</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>14390.33</v>
+        <v>14633.71</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>8855.59</v>
+        <v>9005.360000000001</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2374.6</v>
+        <v>2414.76</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>5534.74</v>
+        <v>5628.35</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>6641.69</v>
+        <v>6754.02</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3320.85</v>
+        <v>3377.01</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2379.94</v>
+        <v>2420.19</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3099.46</v>
+        <v>3151.88</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>6641.69</v>
+        <v>6754.02</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>4427.79</v>
+        <v>4502.68</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2379.94</v>
+        <v>2420.19</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>11069.49</v>
+        <v>11256.7</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>11069.49</v>
+        <v>11256.7</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>11069.49</v>
+        <v>11256.7</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3320.85</v>
+        <v>3354.62</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3652.93</v>
+        <v>3690.08</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>33208.46</v>
+        <v>33546.17</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>7599.2</v>
+        <v>7676.48</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3320.85</v>
+        <v>3354.62</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2545.98</v>
+        <v>2571.87</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>5313.35</v>
+        <v>5367.39</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>3874.32</v>
+        <v>3913.72</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2435.29</v>
+        <v>2460.05</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2767.37</v>
+        <v>2795.51</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>38859.43</v>
+        <v>39254.6</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>11069.49</v>
+        <v>11182.06</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>7332.43</v>
+        <v>7406.99</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3320.85</v>
+        <v>3354.62</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>7748.64</v>
+        <v>7827.44</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>7748.64</v>
+        <v>7827.44</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>7527.25</v>
+        <v>7603.8</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>5269.08</v>
+        <v>5322.66</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>4427.79</v>
+        <v>4472.82</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>9796.5</v>
+        <v>9896.120000000001</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>11366.51</v>
+        <v>11482.1</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2374.6</v>
+        <v>2398.75</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>3874.32</v>
+        <v>3913.72</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>3320.85</v>
+        <v>3354.62</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>3320.85</v>
+        <v>3354.62</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>4195.34</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2344.12</v>
+        <v>2367.96</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>13615.47</v>
+        <v>13753.93</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2435.29</v>
+        <v>2460.05</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>15165.2</v>
+        <v>15319.42</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>27673.72</v>
+        <v>27955.14</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>11069.49</v>
+        <v>11182.06</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>49812.69</v>
+        <v>50319.25</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>5534.74</v>
+        <v>5591.03</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>4970.08</v>
+        <v>5020.63</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>11069.49</v>
+        <v>11182.06</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2435.29</v>
+        <v>2460.05</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>16604.23</v>
+        <v>16773.08</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>9888.700000000001</v>
+        <v>9989.26</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2379.94</v>
+        <v>2402.26</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2435.29</v>
+        <v>2458.13</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>5905.8</v>
+        <v>5961.19</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>4427.79</v>
+        <v>4469.32</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>11069.49</v>
+        <v>11173.31</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>44277.94</v>
+        <v>44693.24</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>13503.33</v>
+        <v>13629.98</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>8855.59</v>
+        <v>8938.65</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>6032.87</v>
+        <v>6089.45</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2545.98</v>
+        <v>2569.86</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3320.85</v>
+        <v>3351.99</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>2435.29</v>
+        <v>2458.13</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>5400.8</v>
+        <v>5451.46</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>3320.85</v>
+        <v>3351.99</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>11069.49</v>
+        <v>11173.31</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>4427.79</v>
+        <v>4469.32</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>2767.37</v>
+        <v>2793.33</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3320.85</v>
+        <v>3351.99</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>4206.4</v>
+        <v>4245.86</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>3874.32</v>
+        <v>3910.66</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>10580.33</v>
+        <v>10679.56</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2767.37</v>
+        <v>2793.33</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>6716.96</v>
+        <v>6779.96</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>63096.07</v>
+        <v>63687.86</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2344.12</v>
+        <v>2366.1</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>22526.4</v>
+        <v>22737.68</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>4427.79</v>
+        <v>4469.32</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>8855.59</v>
+        <v>8938.65</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>61916.45</v>
+        <v>62497.17</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>5534.74</v>
+        <v>5586.65</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>5534.74</v>
+        <v>5586.65</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>11069.49</v>
+        <v>11173.31</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>5534.74</v>
+        <v>5586.65</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>5534.74</v>
+        <v>5586.65</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>6641.69</v>
+        <v>6703.99</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>5534.74</v>
+        <v>5586.65</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>4438.86</v>
+        <v>4480.5</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>5534.74</v>
+        <v>5586.65</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>25964.59</v>
+        <v>26208.11</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2767.37</v>
+        <v>2793.33</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>6641.69</v>
+        <v>6703.99</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>3874.32</v>
+        <v>3910.66</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>3320.85</v>
+        <v>3351.99</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>5534.74</v>
+        <v>5586.65</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>33208.46</v>
+        <v>33519.93</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>4427.79</v>
+        <v>4394.2</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2435.29</v>
+        <v>2416.81</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>3320.85</v>
+        <v>3295.65</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>4427.79</v>
+        <v>4394.2</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>17710.36</v>
+        <v>17576.01</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>8855.59</v>
+        <v>8788.41</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2435.29</v>
+        <v>2416.81</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3890.85</v>
+        <v>3861.33</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>6641.69</v>
+        <v>6591.31</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>22138.97</v>
+        <v>21971.02</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>4427.79</v>
+        <v>4394.2</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>27673.72</v>
+        <v>27463.78</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>7354.55</v>
+        <v>7298.76</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>17157.7</v>
+        <v>17027.54</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>3320.85</v>
+        <v>3295.65</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>4427.79</v>
+        <v>4394.2</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>49812.69</v>
+        <v>49434.8</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>3320.85</v>
+        <v>3295.65</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>3320.85</v>
+        <v>3295.65</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>2767.37</v>
+        <v>2746.38</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>3160.14</v>
+        <v>3136.17</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>39045.84</v>
+        <v>38749.63</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>22138.97</v>
+        <v>21971.02</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>3320.85</v>
+        <v>3295.65</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>11069.49</v>
+        <v>10985.51</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>17659.49</v>
+        <v>17525.52</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>3320.85</v>
+        <v>3295.65</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>22692.45</v>
+        <v>22520.3</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>46491.84</v>
+        <v>46139.14</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>2379.94</v>
+        <v>2361.88</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>8855.59</v>
+        <v>8788.41</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2767.37</v>
+        <v>2720.61</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>16604.23</v>
+        <v>16323.69</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>4427.79</v>
+        <v>4352.98</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>2435.29</v>
+        <v>2394.14</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2767.37</v>
+        <v>2720.61</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>5534.74</v>
+        <v>5441.23</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2374.6</v>
+        <v>2334.48</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>66416.92</v>
+        <v>65294.75</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>3320.85</v>
+        <v>3264.74</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>5534.74</v>
+        <v>5441.23</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>16604.23</v>
+        <v>16323.69</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>20699.94</v>
+        <v>20350.2</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>5534.74</v>
+        <v>5441.23</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>9962.540000000001</v>
+        <v>9794.209999999999</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>6641.69</v>
+        <v>6529.48</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>7637.95</v>
+        <v>7508.9</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>44277.94</v>
+        <v>43529.83</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2545.98</v>
+        <v>2502.97</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2374.6</v>
+        <v>2334.48</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>4427.79</v>
+        <v>4352.98</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2921.7</v>
+        <v>2872.34</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>8302.110000000001</v>
+        <v>8161.84</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>11901.91</v>
+        <v>11700.82</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2435.29</v>
+        <v>2394.14</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>2656.68</v>
+        <v>2611.79</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>3320.85</v>
+        <v>3264.74</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>11069.49</v>
+        <v>10882.46</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>66416.92</v>
+        <v>65294.75</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>16604.23</v>
+        <v>16323.69</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>6641.69</v>
+        <v>6529.48</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>11733.66</v>
+        <v>11535.41</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>5534.74</v>
+        <v>5441.23</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>4427.79</v>
+        <v>4352.98</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>7637.95</v>
+        <v>7508.9</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>34536.8</v>
+        <v>33953.27</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>6641.69</v>
+        <v>6529.48</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>11069.49</v>
+        <v>10882.46</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>6641.69</v>
+        <v>6547.43</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>6740.04</v>
+        <v>6644.39</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>37636.25</v>
+        <v>37102.11</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>3320.85</v>
+        <v>3273.72</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>5534.74</v>
+        <v>5456.19</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>36529.3</v>
+        <v>36010.87</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>5534.74</v>
+        <v>5456.19</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>16604.23</v>
+        <v>16368.58</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>2656.68</v>
+        <v>2618.97</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>8930.1</v>
+        <v>8803.360000000001</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2374.6</v>
+        <v>2340.9</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2435.29</v>
+        <v>2400.72</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>3320.85</v>
+        <v>3273.72</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>5259.59</v>
+        <v>5184.95</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>3099.46</v>
+        <v>3055.47</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>6641.69</v>
+        <v>6547.43</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>8855.59</v>
+        <v>8729.91</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>5534.74</v>
+        <v>5456.19</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>7748.64</v>
+        <v>7638.67</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>11069.49</v>
+        <v>10912.38</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>2435.29</v>
+        <v>2400.72</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>11069.49</v>
+        <v>10912.38</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>11285.62</v>
+        <v>11125.46</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>16604.23</v>
+        <v>16368.58</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>33208.46</v>
+        <v>32737.15</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2435.29</v>
+        <v>2400.72</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>9392.77</v>
+        <v>9259.459999999999</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>3320.85</v>
+        <v>3273.72</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>16604.23</v>
+        <v>16368.58</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>2545.98</v>
+        <v>2509.85</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>3031.23</v>
+        <v>2988.21</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>7195.17</v>
+        <v>7096.3</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>12848.58</v>
+        <v>12672.03</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>2435.29</v>
+        <v>2401.83</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>3320.85</v>
+        <v>3275.22</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2545.98</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>33208.46</v>
+        <v>32752.16</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>3874.32</v>
+        <v>3821.09</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>9962.540000000001</v>
+        <v>9825.65</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>2379.94</v>
+        <v>2347.24</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>2405.24</v>
+        <v>2372.19</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2767.37</v>
+        <v>2729.35</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>25017.04</v>
+        <v>24673.3</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>6641.69</v>
+        <v>6550.43</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>4427.79</v>
+        <v>4366.96</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>2379.94</v>
+        <v>2347.24</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>3119.31</v>
+        <v>3076.45</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2767.37</v>
+        <v>2729.35</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>33208.46</v>
+        <v>32752.16</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>4427.79</v>
+        <v>4366.96</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2767.37</v>
+        <v>2729.35</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>22138.97</v>
+        <v>21834.78</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>24352.87</v>
+        <v>24018.25</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>90769.78999999999</v>
+        <v>89522.58</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>4981.27</v>
+        <v>4912.82</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>14390.33</v>
+        <v>14192.6</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>4815.23</v>
+        <v>4749.06</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2816.5</v>
+        <v>2777.8</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>4427.79</v>
+        <v>4366.96</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>4427.79</v>
+        <v>4366.96</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>3985.02</v>
+        <v>3930.26</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>3320.85</v>
+        <v>3275.22</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>2435.29</v>
+        <v>2401.83</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>8855.59</v>
+        <v>8733.91</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>14390.33</v>
+        <v>14192.6</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>3320.85</v>
+        <v>3275.22</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>3320.85</v>
+        <v>3275.22</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>11901.91</v>
+        <v>11738.38</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>3542.24</v>
+        <v>3493.56</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>3874.32</v>
+        <v>3821.09</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>23245.92</v>
+        <v>22926.52</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>5534.74</v>
+        <v>5458.69</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>22138.97</v>
+        <v>21834.78</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>11069.49</v>
+        <v>10917.39</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>2391.01</v>
+        <v>2358.16</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2374.6</v>
+        <v>2341.98</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>5534.74</v>
+        <v>5458.69</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>3320.85</v>
+        <v>3275.22</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>5534.74</v>
+        <v>5500.43</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>5357.63</v>
+        <v>5324.42</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>19925.08</v>
+        <v>19801.54</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>2377.09</v>
+        <v>2362.35</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>5534.74</v>
+        <v>5500.43</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>3874.32</v>
+        <v>3850.3</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>32109.48</v>
+        <v>31910.41</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>2753.09</v>
+        <v>2736.02</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>11069.49</v>
+        <v>11000.86</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>5313.35</v>
+        <v>5280.41</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>2767.37</v>
+        <v>2750.21</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>5584.67</v>
+        <v>5550.04</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>2435.29</v>
+        <v>2420.19</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>5534.74</v>
+        <v>5500.43</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>2379.94</v>
+        <v>2365.18</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>7748.64</v>
+        <v>7700.6</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>8855.59</v>
+        <v>8800.690000000001</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>4981.27</v>
+        <v>4950.39</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>2379.94</v>
+        <v>2365.18</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>30883.87</v>
+        <v>30692.39</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>3874.32</v>
+        <v>3850.3</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>15497.28</v>
+        <v>15401.2</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>5455.86</v>
+        <v>5422.04</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>13260.84</v>
+        <v>13178.63</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>3874.32</v>
+        <v>3850.3</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>7195.17</v>
+        <v>7150.56</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>4427.79</v>
+        <v>4400.34</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>2374.6</v>
+        <v>2359.88</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>2379.94</v>
+        <v>2365.18</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>3320.85</v>
+        <v>3300.26</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>35422.36</v>
+        <v>35202.75</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>16604.23</v>
+        <v>16501.29</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>7748.64</v>
+        <v>7700.6</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>11069.49</v>
+        <v>11000.86</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>3320.85</v>
+        <v>3300.26</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>8855.59</v>
+        <v>8800.690000000001</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>5534.74</v>
+        <v>5500.43</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>8412.809999999999</v>
+        <v>8360.65</v>
       </c>
     </row>
     <row r="391">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>2435.29</v>
+        <v>2420.19</v>
       </c>
     </row>
     <row r="392">
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>55347.43</v>
+        <v>55598.8</v>
       </c>
     </row>
     <row r="393">
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>123978.24</v>
+        <v>124541.31</v>
       </c>
     </row>
     <row r="394">
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>2435.29</v>
+        <v>2446.35</v>
       </c>
     </row>
     <row r="395">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>33208.46</v>
+        <v>33359.28</v>
       </c>
     </row>
     <row r="396">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>6641.69</v>
+        <v>6671.86</v>
       </c>
     </row>
     <row r="397">
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>7195.17</v>
+        <v>7227.84</v>
       </c>
     </row>
     <row r="398">
@@ -24729,7 +24729,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>40165.49</v>
+        <v>40347.91</v>
       </c>
     </row>
     <row r="399">
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>14526.29</v>
+        <v>14592.26</v>
       </c>
     </row>
     <row r="400">
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>6641.69</v>
+        <v>6671.86</v>
       </c>
     </row>
     <row r="401">
@@ -24912,7 +24912,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>3597.58</v>
+        <v>3613.92</v>
       </c>
     </row>
     <row r="402">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>13283.38</v>
+        <v>13343.71</v>
       </c>
     </row>
     <row r="403">
@@ -25034,7 +25034,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>22138.97</v>
+        <v>22239.52</v>
       </c>
     </row>
     <row r="404">
@@ -25095,7 +25095,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>7030.23</v>
+        <v>7062.16</v>
       </c>
     </row>
     <row r="405">
@@ -25156,7 +25156,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>66416.92</v>
+        <v>66718.56</v>
       </c>
     </row>
     <row r="406">
@@ -25217,7 +25217,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>11069.49</v>
+        <v>11119.76</v>
       </c>
     </row>
     <row r="407">
@@ -25278,7 +25278,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>2435.29</v>
+        <v>2446.35</v>
       </c>
     </row>
     <row r="408">
@@ -25339,7 +25339,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>2379.94</v>
+        <v>2390.75</v>
       </c>
     </row>
     <row r="409">
@@ -25400,7 +25400,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>38743.2</v>
+        <v>38919.16</v>
       </c>
     </row>
     <row r="410">
@@ -25461,7 +25461,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>4427.79</v>
+        <v>4447.9</v>
       </c>
     </row>
     <row r="411">
@@ -25522,7 +25522,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>3874.32</v>
+        <v>3891.92</v>
       </c>
     </row>
     <row r="412">
@@ -25583,7 +25583,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>2374.6</v>
+        <v>2385.39</v>
       </c>
     </row>
     <row r="413">
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2697.65</v>
+        <v>2709.9</v>
       </c>
     </row>
     <row r="414">
@@ -25705,7 +25705,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>2435.29</v>
+        <v>2446.35</v>
       </c>
     </row>
     <row r="415">
@@ -25766,7 +25766,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>2435.29</v>
+        <v>2446.35</v>
       </c>
     </row>
     <row r="416">
@@ -25827,7 +25827,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>2767.37</v>
+        <v>2779.94</v>
       </c>
     </row>
     <row r="417">
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>12176.43</v>
+        <v>12231.74</v>
       </c>
     </row>
     <row r="418">
@@ -25949,7 +25949,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>11069.49</v>
+        <v>11119.76</v>
       </c>
     </row>
     <row r="419">
@@ -26010,7 +26010,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>3874.32</v>
+        <v>3891.92</v>
       </c>
     </row>
     <row r="420">
@@ -26071,7 +26071,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>8855.59</v>
+        <v>8895.809999999999</v>
       </c>
     </row>
     <row r="421">
@@ -26132,7 +26132,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>2435.29</v>
+        <v>2446.35</v>
       </c>
     </row>
     <row r="422">
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>2767.37</v>
+        <v>2779.94</v>
       </c>
     </row>
     <row r="423">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>7748.64</v>
+        <v>7783.83</v>
       </c>
     </row>
     <row r="424">
@@ -26315,7 +26315,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>3652.93</v>
+        <v>3669.52</v>
       </c>
     </row>
     <row r="425">
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>36529.3</v>
+        <v>36695.21</v>
       </c>
     </row>
     <row r="426">
@@ -26437,7 +26437,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>6332.06</v>
+        <v>6360.82</v>
       </c>
     </row>
     <row r="427">
@@ -26498,7 +26498,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>2374.6</v>
+        <v>2385.39</v>
       </c>
     </row>
     <row r="428">
@@ -26559,7 +26559,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>3320.85</v>
+        <v>3370.29</v>
       </c>
     </row>
     <row r="429">
@@ -26620,7 +26620,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>2379.94</v>
+        <v>2415.38</v>
       </c>
     </row>
     <row r="430">
@@ -26681,7 +26681,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>8374.07</v>
+        <v>8498.76</v>
       </c>
     </row>
     <row r="431">
@@ -26742,7 +26742,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>7748.64</v>
+        <v>7864.02</v>
       </c>
     </row>
     <row r="432">
@@ -26803,7 +26803,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>49812.69</v>
+        <v>50554.41</v>
       </c>
     </row>
     <row r="433">
@@ -26864,7 +26864,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>71951.66</v>
+        <v>73023.03999999999</v>
       </c>
     </row>
     <row r="434">
@@ -26925,7 +26925,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>16604.23</v>
+        <v>16851.47</v>
       </c>
     </row>
     <row r="435">
@@ -26986,7 +26986,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>12729.91</v>
+        <v>12919.46</v>
       </c>
     </row>
     <row r="436">
@@ -27047,7 +27047,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>6641.69</v>
+        <v>6740.59</v>
       </c>
     </row>
     <row r="437">
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>3320.85</v>
+        <v>3370.29</v>
       </c>
     </row>
     <row r="438">
@@ -27169,7 +27169,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>2656.68</v>
+        <v>2696.24</v>
       </c>
     </row>
     <row r="439">
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>8302.110000000001</v>
+        <v>8425.74</v>
       </c>
     </row>
     <row r="440">
@@ -27291,7 +27291,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>38743.2</v>
+        <v>39320.1</v>
       </c>
     </row>
     <row r="441">
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>11228.89</v>
+        <v>11396.09</v>
       </c>
     </row>
     <row r="442">
@@ -27413,7 +27413,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>2435.29</v>
+        <v>2471.55</v>
       </c>
     </row>
     <row r="443">
@@ -27474,7 +27474,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>16604.23</v>
+        <v>16851.47</v>
       </c>
     </row>
     <row r="444">
@@ -27535,7 +27535,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>2767.37</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="445">
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>9397.99</v>
+        <v>9537.93</v>
       </c>
     </row>
     <row r="446">
@@ -27657,7 +27657,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>8302.110000000001</v>
+        <v>8425.74</v>
       </c>
     </row>
     <row r="447">
@@ -27718,7 +27718,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>11069.49</v>
+        <v>11234.31</v>
       </c>
     </row>
     <row r="448">
@@ -27779,7 +27779,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>22138.97</v>
+        <v>22468.63</v>
       </c>
     </row>
     <row r="449">
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>11069.49</v>
+        <v>11234.31</v>
       </c>
     </row>
     <row r="450">
@@ -27901,7 +27901,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>11069.49</v>
+        <v>11234.31</v>
       </c>
     </row>
     <row r="451">
@@ -27962,7 +27962,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>2767.37</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="452">
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>5534.74</v>
+        <v>5617.16</v>
       </c>
     </row>
     <row r="453">
@@ -28084,7 +28084,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>8302.110000000001</v>
+        <v>8425.74</v>
       </c>
     </row>
     <row r="454">
@@ -28145,7 +28145,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>3210.15</v>
+        <v>3257.95</v>
       </c>
     </row>
     <row r="455">
@@ -28206,7 +28206,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>2767.37</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="456">
@@ -28267,7 +28267,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>4576.21</v>
+        <v>4644.35</v>
       </c>
     </row>
     <row r="457">
@@ -28328,7 +28328,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>35422.36</v>
+        <v>35949.81</v>
       </c>
     </row>
     <row r="458">
@@ -28389,7 +28389,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>5534.74</v>
+        <v>5617.16</v>
       </c>
     </row>
     <row r="459">
@@ -28450,7 +28450,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>2375.51</v>
+        <v>2410.88</v>
       </c>
     </row>
     <row r="460">
@@ -28511,7 +28511,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>2374.6</v>
+        <v>2409.96</v>
       </c>
     </row>
     <row r="461">
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>3320.85</v>
+        <v>3370.29</v>
       </c>
     </row>
     <row r="462">
@@ -28633,7 +28633,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>3874.32</v>
+        <v>3932.01</v>
       </c>
     </row>
     <row r="463">
@@ -28694,7 +28694,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>5534.74</v>
+        <v>5617.16</v>
       </c>
     </row>
     <row r="464">
@@ -28755,7 +28755,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>5534.74</v>
+        <v>5617.16</v>
       </c>
     </row>
     <row r="465">
@@ -28816,7 +28816,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>4427.79</v>
+        <v>4493.73</v>
       </c>
     </row>
     <row r="466">
@@ -28877,7 +28877,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>5534.74</v>
+        <v>5617.16</v>
       </c>
     </row>
     <row r="467">
@@ -28938,7 +28938,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>5534.74</v>
+        <v>5617.16</v>
       </c>
     </row>
     <row r="468">
@@ -28999,7 +28999,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>2775.64</v>
+        <v>2816.97</v>
       </c>
     </row>
     <row r="469">
@@ -29060,7 +29060,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>8855.59</v>
+        <v>8987.450000000001</v>
       </c>
     </row>
     <row r="470">
@@ -29121,7 +29121,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>2767.37</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="471">
@@ -29182,7 +29182,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>2608.86</v>
+        <v>2647.7</v>
       </c>
     </row>
     <row r="472">
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>4427.79</v>
+        <v>4493.73</v>
       </c>
     </row>
     <row r="473">
@@ -29304,7 +29304,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>16604.23</v>
+        <v>16851.47</v>
       </c>
     </row>
     <row r="474">
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>4427.79</v>
+        <v>4493.73</v>
       </c>
     </row>
     <row r="475">
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>22138.97</v>
+        <v>22468.63</v>
       </c>
     </row>
     <row r="476">
@@ -29487,7 +29487,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>16604.23</v>
+        <v>16851.47</v>
       </c>
     </row>
     <row r="477">
@@ -29548,7 +29548,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>35422.36</v>
+        <v>36095.79</v>
       </c>
     </row>
     <row r="478">
@@ -29609,7 +29609,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>66416.92</v>
+        <v>67679.60000000001</v>
       </c>
     </row>
     <row r="479">
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>4095.71</v>
+        <v>4173.58</v>
       </c>
     </row>
     <row r="480">
@@ -29731,7 +29731,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>4427.79</v>
+        <v>4511.97</v>
       </c>
     </row>
     <row r="481">
@@ -29792,7 +29792,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>22138.97</v>
+        <v>22559.87</v>
       </c>
     </row>
     <row r="482">
@@ -29853,7 +29853,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>2379.94</v>
+        <v>2425.19</v>
       </c>
     </row>
     <row r="483">
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>4461</v>
+        <v>4545.81</v>
       </c>
     </row>
     <row r="484">
@@ -29975,7 +29975,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>2878.07</v>
+        <v>2932.78</v>
       </c>
     </row>
     <row r="485">
@@ -30036,7 +30036,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>3320.85</v>
+        <v>3383.98</v>
       </c>
     </row>
     <row r="486">
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>6641.69</v>
+        <v>6767.96</v>
       </c>
     </row>
     <row r="487">
@@ -30158,7 +30158,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>2435.29</v>
+        <v>2481.59</v>
       </c>
     </row>
     <row r="488">
@@ -30219,7 +30219,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>4427.79</v>
+        <v>4511.97</v>
       </c>
     </row>
     <row r="489">
@@ -30280,7 +30280,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>7805.09</v>
+        <v>7953.48</v>
       </c>
     </row>
     <row r="490">
@@ -30341,7 +30341,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>33208.46</v>
+        <v>33839.8</v>
       </c>
     </row>
     <row r="491">
@@ -30402,7 +30402,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>2822.72</v>
+        <v>2876.38</v>
       </c>
     </row>
     <row r="492">
@@ -30463,7 +30463,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>2374.6</v>
+        <v>2419.75</v>
       </c>
     </row>
     <row r="493">
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>4322.56</v>
+        <v>4404.74</v>
       </c>
     </row>
     <row r="494">
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>6641.69</v>
+        <v>6767.96</v>
       </c>
     </row>
     <row r="495">
@@ -30646,7 +30646,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>2767.37</v>
+        <v>2819.98</v>
       </c>
     </row>
     <row r="496">
@@ -30707,7 +30707,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>4122.28</v>
+        <v>4200.65</v>
       </c>
     </row>
     <row r="497">
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>5508.24</v>
+        <v>5612.96</v>
       </c>
     </row>
     <row r="498">
@@ -30829,7 +30829,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>11901.91</v>
+        <v>12128.19</v>
       </c>
     </row>
     <row r="499">
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>22138.97</v>
+        <v>22559.87</v>
       </c>
     </row>
     <row r="500">
@@ -30951,7 +30951,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>66416.92</v>
+        <v>67679.60000000001</v>
       </c>
     </row>
     <row r="501">
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>5269.08</v>
+        <v>5369.25</v>
       </c>
     </row>
     <row r="502">
@@ -31073,7 +31073,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>2435.29</v>
+        <v>2481.59</v>
       </c>
     </row>
     <row r="503">
@@ -31134,7 +31134,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>2645.61</v>
+        <v>2695.9</v>
       </c>
     </row>
     <row r="504">
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>3099.46</v>
+        <v>3158.38</v>
       </c>
     </row>
     <row r="505">
@@ -31256,7 +31256,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>7915.35</v>
+        <v>8065.83</v>
       </c>
     </row>
     <row r="506">
@@ -31317,7 +31317,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>23522.66</v>
+        <v>23969.86</v>
       </c>
     </row>
     <row r="507">
@@ -31378,7 +31378,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>4427.79</v>
+        <v>4511.97</v>
       </c>
     </row>
     <row r="508">
@@ -31439,7 +31439,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>3320.85</v>
+        <v>3383.98</v>
       </c>
     </row>
     <row r="509">
@@ -31500,7 +31500,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>39407.37</v>
+        <v>40156.57</v>
       </c>
     </row>
     <row r="510">
@@ -31561,7 +31561,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>11069.49</v>
+        <v>11279.93</v>
       </c>
     </row>
     <row r="511">
@@ -31622,7 +31622,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>2435.29</v>
+        <v>2481.59</v>
       </c>
     </row>
     <row r="512">
@@ -31683,7 +31683,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>4427.79</v>
+        <v>4511.97</v>
       </c>
     </row>
     <row r="513">
@@ -31744,7 +31744,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>2379.94</v>
+        <v>2425.19</v>
       </c>
     </row>
     <row r="514">
@@ -31805,7 +31805,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>12176.43</v>
+        <v>12407.93</v>
       </c>
     </row>
     <row r="515">
@@ -31866,7 +31866,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>2553.79</v>
+        <v>2602.34</v>
       </c>
     </row>
     <row r="516">
@@ -31927,7 +31927,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>2374.63</v>
+        <v>2419.77</v>
       </c>
     </row>
     <row r="517">
@@ -31988,7 +31988,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>3320.85</v>
+        <v>3383.98</v>
       </c>
     </row>
     <row r="518">
@@ -32049,7 +32049,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>5534.74</v>
+        <v>5639.97</v>
       </c>
     </row>
     <row r="519">
@@ -32110,7 +32110,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>6641.69</v>
+        <v>6767.96</v>
       </c>
     </row>
     <row r="520">
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>2712.02</v>
+        <v>2763.58</v>
       </c>
     </row>
     <row r="521">
@@ -32232,7 +32232,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>33208.46</v>
+        <v>33839.8</v>
       </c>
     </row>
     <row r="522">
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>7865.62</v>
+        <v>8043.01</v>
       </c>
     </row>
     <row r="523">
@@ -32354,7 +32354,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>5822.55</v>
+        <v>5953.86</v>
       </c>
     </row>
     <row r="524">
@@ -32415,7 +32415,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>23061.06</v>
+        <v>23581.15</v>
       </c>
     </row>
     <row r="525">
@@ -32476,7 +32476,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>27673.72</v>
+        <v>28297.83</v>
       </c>
     </row>
     <row r="526">
@@ -32537,7 +32537,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>3034.12</v>
+        <v>3102.54</v>
       </c>
     </row>
     <row r="527">
@@ -32598,7 +32598,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>2379.94</v>
+        <v>2433.61</v>
       </c>
     </row>
     <row r="528">
@@ -32659,7 +32659,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>7199.59</v>
+        <v>7361.96</v>
       </c>
     </row>
     <row r="529">
@@ -32720,7 +32720,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>6818.8</v>
+        <v>6972.59</v>
       </c>
     </row>
     <row r="530">
@@ -32781,7 +32781,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>37082.78</v>
+        <v>37919.09</v>
       </c>
     </row>
     <row r="531">
@@ -32842,7 +32842,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>22138.97</v>
+        <v>22638.26</v>
       </c>
     </row>
     <row r="532">
@@ -32903,7 +32903,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>4738.34</v>
+        <v>4845.2</v>
       </c>
     </row>
     <row r="533">
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>6641.69</v>
+        <v>6791.48</v>
       </c>
     </row>
     <row r="534">
@@ -33025,7 +33025,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>2379.94</v>
+        <v>2433.61</v>
       </c>
     </row>
     <row r="535">
@@ -33086,7 +33086,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>2374.6</v>
+        <v>2428.16</v>
       </c>
     </row>
     <row r="536">
@@ -33147,7 +33147,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>3874.32</v>
+        <v>3961.7</v>
       </c>
     </row>
     <row r="537">
@@ -33208,7 +33208,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>3985.02</v>
+        <v>4074.89</v>
       </c>
     </row>
     <row r="538">
@@ -33269,7 +33269,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>3320.85</v>
+        <v>3395.74</v>
       </c>
     </row>
     <row r="539">
@@ -33330,7 +33330,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>5091.96</v>
+        <v>5206.8</v>
       </c>
     </row>
     <row r="540">
@@ -33391,7 +33391,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>2379.94</v>
+        <v>2433.61</v>
       </c>
     </row>
     <row r="541">
@@ -33452,7 +33452,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>5534.74</v>
+        <v>5659.57</v>
       </c>
     </row>
     <row r="542">
@@ -33513,7 +33513,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>2767.37</v>
+        <v>2829.78</v>
       </c>
     </row>
     <row r="543">
@@ -33574,7 +33574,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>7159.99</v>
+        <v>7321.46</v>
       </c>
     </row>
     <row r="544">
@@ -33635,7 +33635,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>11069.49</v>
+        <v>11319.13</v>
       </c>
     </row>
     <row r="545">
@@ -33696,7 +33696,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>3320.85</v>
+        <v>3395.74</v>
       </c>
     </row>
     <row r="546">
@@ -33757,7 +33757,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>33208.46</v>
+        <v>33957.39</v>
       </c>
     </row>
     <row r="547">
@@ -33818,7 +33818,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>6641.69</v>
+        <v>6791.48</v>
       </c>
     </row>
     <row r="548">
@@ -33879,7 +33879,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>2767.37</v>
+        <v>2829.78</v>
       </c>
     </row>
     <row r="549">
@@ -33940,7 +33940,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>5534.74</v>
+        <v>5659.57</v>
       </c>
     </row>
     <row r="550">
@@ -34001,7 +34001,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>5534.74</v>
+        <v>5659.57</v>
       </c>
     </row>
     <row r="551">
@@ -34062,7 +34062,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>3320.85</v>
+        <v>3395.74</v>
       </c>
     </row>
     <row r="552">
@@ -34123,7 +34123,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>26013.27</v>
+        <v>26599.94</v>
       </c>
     </row>
     <row r="553">
@@ -34184,7 +34184,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>3320.85</v>
+        <v>3395.74</v>
       </c>
     </row>
     <row r="554">
@@ -34245,7 +34245,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>3320.85</v>
+        <v>3395.74</v>
       </c>
     </row>
     <row r="555">
@@ -34306,7 +34306,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>16604.23</v>
+        <v>16978.7</v>
       </c>
     </row>
     <row r="556">
@@ -34367,7 +34367,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>11069.49</v>
+        <v>11145.91</v>
       </c>
     </row>
     <row r="557">
@@ -34428,7 +34428,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>13836.86</v>
+        <v>13932.39</v>
       </c>
     </row>
     <row r="558">
@@ -34489,7 +34489,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>6641.69</v>
+        <v>6687.55</v>
       </c>
     </row>
     <row r="559">
@@ -34550,7 +34550,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>11069.49</v>
+        <v>11145.91</v>
       </c>
     </row>
     <row r="560">
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>3320.85</v>
+        <v>3343.77</v>
       </c>
     </row>
     <row r="561">
@@ -34672,7 +34672,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>27673.72</v>
+        <v>27864.78</v>
       </c>
     </row>
     <row r="562">
@@ -34733,7 +34733,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>26566.77</v>
+        <v>26750.19</v>
       </c>
     </row>
     <row r="563">
@@ -34794,7 +34794,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>3763.63</v>
+        <v>3789.61</v>
       </c>
     </row>
     <row r="564">
@@ -34855,7 +34855,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>6641.69</v>
+        <v>6687.55</v>
       </c>
     </row>
     <row r="565">
@@ -34916,7 +34916,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>7748.64</v>
+        <v>7802.14</v>
       </c>
     </row>
     <row r="566">
@@ -34977,7 +34977,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>2374.6</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="567">
@@ -35038,7 +35038,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>6641.69</v>
+        <v>6687.55</v>
       </c>
     </row>
     <row r="568">
@@ -35099,7 +35099,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>25459.82</v>
+        <v>25635.6</v>
       </c>
     </row>
     <row r="569">
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>15497.28</v>
+        <v>15604.28</v>
       </c>
     </row>
     <row r="570">
@@ -35221,7 +35221,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>2435.29</v>
+        <v>2452.1</v>
       </c>
     </row>
     <row r="571">
@@ -35282,7 +35282,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>2374.6</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="572">
@@ -35343,7 +35343,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>11069.49</v>
+        <v>11145.91</v>
       </c>
     </row>
     <row r="573">
@@ -35469,7 +35469,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>11069.49</v>
+        <v>11145.91</v>
       </c>
     </row>
     <row r="575">
@@ -35530,7 +35530,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>3320.85</v>
+        <v>3343.77</v>
       </c>
     </row>
     <row r="576">
@@ -35591,7 +35591,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>9962.540000000001</v>
+        <v>10031.32</v>
       </c>
     </row>
     <row r="577">
@@ -35652,7 +35652,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>11629.63</v>
+        <v>11709.93</v>
       </c>
     </row>
     <row r="578">
@@ -35713,7 +35713,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>2435.29</v>
+        <v>2452.1</v>
       </c>
     </row>
     <row r="579">
@@ -35774,7 +35774,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>11506.73</v>
+        <v>11586.17</v>
       </c>
     </row>
     <row r="580">
@@ -35835,7 +35835,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>2374.6</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="581">
@@ -35896,7 +35896,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>2374.6</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="582">
@@ -35957,7 +35957,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>16604.23</v>
+        <v>16718.87</v>
       </c>
     </row>
     <row r="583">
@@ -36018,7 +36018,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>4427.79</v>
+        <v>4458.36</v>
       </c>
     </row>
     <row r="584">
@@ -36079,7 +36079,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>3320.85</v>
+        <v>3343.77</v>
       </c>
     </row>
     <row r="585">
@@ -36140,7 +36140,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>38743.2</v>
+        <v>39010.69</v>
       </c>
     </row>
     <row r="586">
@@ -36201,7 +36201,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>11069.49</v>
+        <v>11145.91</v>
       </c>
     </row>
     <row r="587">
@@ -36262,7 +36262,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>2767.37</v>
+        <v>2786.48</v>
       </c>
     </row>
     <row r="588">
@@ -36323,7 +36323,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>32278.62</v>
+        <v>32501.48</v>
       </c>
     </row>
     <row r="589">
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>2379.94</v>
+        <v>2387.3</v>
       </c>
     </row>
     <row r="590">
@@ -36445,7 +36445,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>11069.49</v>
+        <v>11103.71</v>
       </c>
     </row>
     <row r="591">
@@ -36506,7 +36506,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>2379.94</v>
+        <v>2387.3</v>
       </c>
     </row>
     <row r="592">
@@ -36567,7 +36567,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>23245.92</v>
+        <v>23317.79</v>
       </c>
     </row>
     <row r="593">
@@ -36628,7 +36628,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>22138.97</v>
+        <v>22207.42</v>
       </c>
     </row>
     <row r="594">
@@ -36689,7 +36689,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>16604.23</v>
+        <v>16655.56</v>
       </c>
     </row>
     <row r="595">
@@ -36750,7 +36750,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>3797.91</v>
+        <v>3809.65</v>
       </c>
     </row>
     <row r="596">
@@ -36811,7 +36811,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>7915.35</v>
+        <v>7939.82</v>
       </c>
     </row>
     <row r="597">
@@ -36872,7 +36872,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>4981.27</v>
+        <v>4996.67</v>
       </c>
     </row>
     <row r="598">
@@ -36933,7 +36933,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>2379.94</v>
+        <v>2387.3</v>
       </c>
     </row>
     <row r="599">
@@ -36994,7 +36994,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>9741.15</v>
+        <v>9771.26</v>
       </c>
     </row>
     <row r="600">
@@ -37055,7 +37055,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>3099.46</v>
+        <v>3109.04</v>
       </c>
     </row>
     <row r="601">
@@ -37116,7 +37116,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>3320.85</v>
+        <v>3331.11</v>
       </c>
     </row>
     <row r="602">
@@ -37177,7 +37177,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>5534.74</v>
+        <v>5551.85</v>
       </c>
     </row>
     <row r="603">
@@ -37238,7 +37238,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>11069.49</v>
+        <v>11103.71</v>
       </c>
     </row>
     <row r="604">
@@ -37299,7 +37299,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>5534.74</v>
+        <v>5551.85</v>
       </c>
     </row>
     <row r="605">
@@ -37360,7 +37360,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>2656.68</v>
+        <v>2664.89</v>
       </c>
     </row>
     <row r="606">
@@ -37421,7 +37421,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>7748.64</v>
+        <v>7772.6</v>
       </c>
     </row>
     <row r="607">
@@ -37482,7 +37482,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>2712.02</v>
+        <v>2720.41</v>
       </c>
     </row>
     <row r="608">
@@ -37543,7 +37543,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>2988.76</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="609">
@@ -37604,7 +37604,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>3320.85</v>
+        <v>3331.11</v>
       </c>
     </row>
     <row r="610">
@@ -37665,7 +37665,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>7527.25</v>
+        <v>7550.52</v>
       </c>
     </row>
     <row r="611">
@@ -37726,7 +37726,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>6641.69</v>
+        <v>6662.23</v>
       </c>
     </row>
     <row r="612">
@@ -37787,7 +37787,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>2435.29</v>
+        <v>2442.82</v>
       </c>
     </row>
     <row r="613">
@@ -37848,7 +37848,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>78361.92999999999</v>
+        <v>78604.2</v>
       </c>
     </row>
     <row r="614">
@@ -37909,7 +37909,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>12847.25</v>
+        <v>12886.96</v>
       </c>
     </row>
     <row r="615">
@@ -37970,7 +37970,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>2379.94</v>
+        <v>2387.3</v>
       </c>
     </row>
     <row r="616">
@@ -38031,7 +38031,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>7748.64</v>
+        <v>7772.6</v>
       </c>
     </row>
     <row r="617">
@@ -38092,7 +38092,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>11069.49</v>
+        <v>11103.71</v>
       </c>
     </row>
     <row r="618">
@@ -38153,7 +38153,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>2624.58</v>
+        <v>2632.69</v>
       </c>
     </row>
     <row r="619">
@@ -38214,7 +38214,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>4427.79</v>
+        <v>4441.48</v>
       </c>
     </row>
     <row r="620">
@@ -38275,7 +38275,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>6785.43</v>
+        <v>6806.41</v>
       </c>
     </row>
     <row r="621">
@@ -38336,7 +38336,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>2379.94</v>
+        <v>2387.3</v>
       </c>
     </row>
     <row r="622">
@@ -38397,7 +38397,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>5837.35</v>
+        <v>5821.91</v>
       </c>
     </row>
     <row r="623">
@@ -38458,7 +38458,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>5530.92</v>
+        <v>5516.29</v>
       </c>
     </row>
     <row r="624">
@@ -38519,7 +38519,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>6487.11</v>
+        <v>6469.95</v>
       </c>
     </row>
     <row r="625">
@@ -38580,7 +38580,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>10091.05</v>
+        <v>10064.36</v>
       </c>
     </row>
     <row r="626">
@@ -38641,7 +38641,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>6204.63</v>
+        <v>6188.22</v>
       </c>
     </row>
     <row r="627">
@@ -38702,7 +38702,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>3542.24</v>
+        <v>3532.87</v>
       </c>
     </row>
     <row r="628">
@@ -38763,7 +38763,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>2767.37</v>
+        <v>2760.05</v>
       </c>
     </row>
     <row r="629">
@@ -38824,7 +38824,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>5534.74</v>
+        <v>5520.1</v>
       </c>
     </row>
     <row r="630">
@@ -38885,7 +38885,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>20914.81</v>
+        <v>20859.5</v>
       </c>
     </row>
     <row r="631">
@@ -38946,7 +38946,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>3874.32</v>
+        <v>3864.07</v>
       </c>
     </row>
     <row r="632">
@@ -39007,7 +39007,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>2379.94</v>
+        <v>2373.64</v>
       </c>
     </row>
     <row r="633">
@@ -39068,7 +39068,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>17711.18</v>
+        <v>17664.33</v>
       </c>
     </row>
     <row r="634">
@@ -39129,7 +39129,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>24133.61</v>
+        <v>24069.78</v>
       </c>
     </row>
     <row r="635">
@@ -39190,7 +39190,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>11069.49</v>
+        <v>11040.21</v>
       </c>
     </row>
     <row r="636">
@@ -39251,7 +39251,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>3237.45</v>
+        <v>3228.88</v>
       </c>
     </row>
     <row r="637">
@@ -39312,7 +39312,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>7207.9</v>
+        <v>7188.83</v>
       </c>
     </row>
     <row r="638">
@@ -39373,7 +39373,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>4427.79</v>
+        <v>4416.08</v>
       </c>
     </row>
     <row r="639">
@@ -39434,7 +39434,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>3320.85</v>
+        <v>3312.06</v>
       </c>
     </row>
     <row r="640">
@@ -39495,7 +39495,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>5534.74</v>
+        <v>5520.1</v>
       </c>
     </row>
     <row r="641">
@@ -39556,7 +39556,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>3320.85</v>
+        <v>3312.06</v>
       </c>
     </row>
     <row r="642">
@@ -39617,7 +39617,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>33208.46</v>
+        <v>33120.63</v>
       </c>
     </row>
     <row r="643">
@@ -39678,7 +39678,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>7748.64</v>
+        <v>7728.15</v>
       </c>
     </row>
     <row r="644">
@@ -39739,7 +39739,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>11003.07</v>
+        <v>10973.97</v>
       </c>
     </row>
     <row r="645">
@@ -39800,7 +39800,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>4427.79</v>
+        <v>4416.08</v>
       </c>
     </row>
     <row r="646">
@@ -39861,7 +39861,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>3320.85</v>
+        <v>3312.06</v>
       </c>
     </row>
     <row r="647">
@@ -39922,7 +39922,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>2767.37</v>
+        <v>2760.05</v>
       </c>
     </row>
     <row r="648">
@@ -39983,7 +39983,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>2767.37</v>
+        <v>2760.05</v>
       </c>
     </row>
     <row r="649">
@@ -40044,7 +40044,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>6641.69</v>
+        <v>6624.13</v>
       </c>
     </row>
     <row r="650">
@@ -40105,7 +40105,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>23245.92</v>
+        <v>23184.44</v>
       </c>
     </row>
     <row r="651">
@@ -40166,7 +40166,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>5534.74</v>
+        <v>5520.1</v>
       </c>
     </row>
     <row r="652">
@@ -40227,7 +40227,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>3320.85</v>
+        <v>3312.06</v>
       </c>
     </row>
     <row r="653">
@@ -40288,7 +40288,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>6641.69</v>
+        <v>6624.13</v>
       </c>
     </row>
     <row r="654">
@@ -40349,7 +40349,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>6749.7</v>
+        <v>6659.79</v>
       </c>
     </row>
     <row r="655">
@@ -40410,7 +40410,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>4652.51</v>
+        <v>4590.53</v>
       </c>
     </row>
     <row r="656">
@@ -40471,7 +40471,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>2435.29</v>
+        <v>2402.85</v>
       </c>
     </row>
     <row r="657">
@@ -40532,7 +40532,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>2379.94</v>
+        <v>2348.24</v>
       </c>
     </row>
     <row r="658">
@@ -40593,7 +40593,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>26961.95</v>
+        <v>26602.81</v>
       </c>
     </row>
     <row r="659">
@@ -40654,7 +40654,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>5252.47</v>
+        <v>5182.51</v>
       </c>
     </row>
     <row r="660">
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>2452.21</v>
+        <v>2419.55</v>
       </c>
     </row>
     <row r="661">
@@ -40776,7 +40776,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>4427.79</v>
+        <v>4368.82</v>
       </c>
     </row>
     <row r="662">
@@ -40837,7 +40837,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>25459.82</v>
+        <v>25120.69</v>
       </c>
     </row>
     <row r="663">
@@ -40898,7 +40898,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>3320.85</v>
+        <v>3276.61</v>
       </c>
     </row>
     <row r="664">
@@ -40959,7 +40959,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>22138.97</v>
+        <v>21844.08</v>
       </c>
     </row>
     <row r="665">
@@ -41020,7 +41020,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>2767.37</v>
+        <v>2730.51</v>
       </c>
     </row>
     <row r="666">
@@ -41081,7 +41081,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>7748.64</v>
+        <v>7645.43</v>
       </c>
     </row>
     <row r="667">
@@ -41142,7 +41142,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>7748.64</v>
+        <v>7645.43</v>
       </c>
     </row>
     <row r="668">
@@ -41203,7 +41203,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>3320.85</v>
+        <v>3276.61</v>
       </c>
     </row>
     <row r="669">
@@ -41264,7 +41264,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>6641.69</v>
+        <v>6553.22</v>
       </c>
     </row>
     <row r="670">
@@ -41325,7 +41325,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>2435.29</v>
+        <v>2402.85</v>
       </c>
     </row>
     <row r="671">
@@ -41386,7 +41386,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>17711.18</v>
+        <v>17475.26</v>
       </c>
     </row>
     <row r="672">
@@ -41447,7 +41447,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>2849.29</v>
+        <v>2811.33</v>
       </c>
     </row>
     <row r="673">
@@ -41508,7 +41508,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>22138.97</v>
+        <v>21844.08</v>
       </c>
     </row>
     <row r="674">
@@ -41569,7 +41569,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>21032.02</v>
+        <v>20751.87</v>
       </c>
     </row>
     <row r="675">
@@ -41630,7 +41630,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>5534.74</v>
+        <v>5461.02</v>
       </c>
     </row>
     <row r="676">
@@ -41691,7 +41691,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>2513.88</v>
+        <v>2480.39</v>
       </c>
     </row>
     <row r="677">
@@ -41752,7 +41752,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>9962.540000000001</v>
+        <v>9829.83</v>
       </c>
     </row>
     <row r="678">
@@ -41813,7 +41813,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>3320.85</v>
+        <v>3276.61</v>
       </c>
     </row>
     <row r="679">
@@ -41874,7 +41874,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>3320.85</v>
+        <v>3276.61</v>
       </c>
     </row>
     <row r="680">
@@ -41935,7 +41935,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>55347.43</v>
+        <v>54610.19</v>
       </c>
     </row>
     <row r="681">
@@ -41996,7 +41996,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>2375.51</v>
+        <v>2343.87</v>
       </c>
     </row>
     <row r="682">
@@ -42057,7 +42057,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>2379.94</v>
+        <v>2348.24</v>
       </c>
     </row>
     <row r="683">
@@ -42118,7 +42118,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>3320.85</v>
+        <v>3276.61</v>
       </c>
     </row>
     <row r="684">
@@ -42179,7 +42179,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>3320.85</v>
+        <v>3276.61</v>
       </c>
     </row>
     <row r="685">
@@ -42240,7 +42240,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>5534.74</v>
+        <v>5461.02</v>
       </c>
     </row>
     <row r="686">
@@ -42301,7 +42301,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>5534.74</v>
+        <v>5461.02</v>
       </c>
     </row>
     <row r="687">
@@ -42362,7 +42362,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>3320.85</v>
+        <v>3276.61</v>
       </c>
     </row>
     <row r="688">
@@ -42423,7 +42423,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>3210.15</v>
+        <v>3167.39</v>
       </c>
     </row>
     <row r="689">
@@ -42484,7 +42484,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>7748.64</v>
+        <v>7645.43</v>
       </c>
     </row>
     <row r="690">
@@ -42545,7 +42545,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>11069.49</v>
+        <v>10922.04</v>
       </c>
     </row>
     <row r="691">
@@ -42606,7 +42606,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>14038.43</v>
+        <v>13851.44</v>
       </c>
     </row>
     <row r="692">
@@ -42667,7 +42667,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>4040.36</v>
+        <v>3986.54</v>
       </c>
     </row>
     <row r="693">
@@ -42728,7 +42728,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>2379.94</v>
+        <v>2348.24</v>
       </c>
     </row>
     <row r="694">
@@ -42789,7 +42789,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>2374.6</v>
+        <v>2342.97</v>
       </c>
     </row>
     <row r="695">
@@ -42850,7 +42850,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>2379.94</v>
+        <v>2348.24</v>
       </c>
     </row>
     <row r="696">
@@ -42911,7 +42911,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>24795.65</v>
+        <v>24465.37</v>
       </c>
     </row>
     <row r="697">
@@ -42972,7 +42972,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>22138.97</v>
+        <v>21844.08</v>
       </c>
     </row>
     <row r="698">
@@ -43033,7 +43033,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>8855.59</v>
+        <v>8737.629999999999</v>
       </c>
     </row>
     <row r="699">
@@ -43094,7 +43094,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>2878.07</v>
+        <v>2821.73</v>
       </c>
     </row>
     <row r="700">
@@ -43155,7 +43155,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>2754.09</v>
+        <v>2700.18</v>
       </c>
     </row>
     <row r="701">
@@ -43216,7 +43216,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>6641.69</v>
+        <v>6511.69</v>
       </c>
     </row>
     <row r="702">
@@ -43277,7 +43277,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>3099.46</v>
+        <v>3038.79</v>
       </c>
     </row>
     <row r="703">
@@ -43338,7 +43338,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>2374.6</v>
+        <v>2328.12</v>
       </c>
     </row>
     <row r="704">
@@ -43399,7 +43399,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>3320.85</v>
+        <v>3255.84</v>
       </c>
     </row>
     <row r="705">
@@ -43460,7 +43460,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>6641.69</v>
+        <v>6511.69</v>
       </c>
     </row>
     <row r="706">
@@ -43521,7 +43521,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>2767.37</v>
+        <v>2713.2</v>
       </c>
     </row>
     <row r="707">
@@ -43582,7 +43582,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>2435.29</v>
+        <v>2387.62</v>
       </c>
     </row>
     <row r="708">
@@ -43643,7 +43643,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>39576.51</v>
+        <v>38801.85</v>
       </c>
     </row>
     <row r="709">
@@ -43704,7 +43704,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>6641.69</v>
+        <v>6511.69</v>
       </c>
     </row>
     <row r="710">
@@ -43765,7 +43765,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>66416.92</v>
+        <v>65116.88</v>
       </c>
     </row>
     <row r="711">
@@ -43826,7 +43826,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>29887.61</v>
+        <v>29302.6</v>
       </c>
     </row>
     <row r="712">
@@ -43887,7 +43887,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>5534.74</v>
+        <v>5426.41</v>
       </c>
     </row>
     <row r="713">
@@ -43948,7 +43948,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>3874.32</v>
+        <v>3798.48</v>
       </c>
     </row>
     <row r="714">
@@ -44009,7 +44009,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>11069.49</v>
+        <v>10852.81</v>
       </c>
     </row>
     <row r="715">
@@ -44070,7 +44070,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>7748.64</v>
+        <v>7596.97</v>
       </c>
     </row>
     <row r="716">
@@ -44131,7 +44131,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>3320.85</v>
+        <v>3255.84</v>
       </c>
     </row>
     <row r="717">
@@ -44192,7 +44192,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>2767.37</v>
+        <v>2713.2</v>
       </c>
     </row>
     <row r="718">
@@ -44253,7 +44253,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>11069.49</v>
+        <v>10852.81</v>
       </c>
     </row>
     <row r="719">
@@ -44314,7 +44314,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>2435.29</v>
+        <v>2387.62</v>
       </c>
     </row>
     <row r="720">
@@ -44375,7 +44375,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>11069.49</v>
+        <v>10852.81</v>
       </c>
     </row>
     <row r="721">
@@ -44436,7 +44436,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>3320.85</v>
+        <v>3255.84</v>
       </c>
     </row>
     <row r="722">
@@ -44497,7 +44497,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>2396.74</v>
+        <v>2349.83</v>
       </c>
     </row>
     <row r="723">
@@ -44558,7 +44558,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>22138.97</v>
+        <v>21705.63</v>
       </c>
     </row>
     <row r="724">
@@ -44619,7 +44619,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>8302.110000000001</v>
+        <v>8139.61</v>
       </c>
     </row>
     <row r="725">
@@ -44680,7 +44680,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>18818.13</v>
+        <v>18449.78</v>
       </c>
     </row>
     <row r="726">
@@ -44741,7 +44741,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>11069.49</v>
+        <v>10852.81</v>
       </c>
     </row>
     <row r="727">
@@ -44802,7 +44802,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>11069.49</v>
+        <v>10852.81</v>
       </c>
     </row>
     <row r="728">
@@ -44863,7 +44863,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>3962.88</v>
+        <v>3885.31</v>
       </c>
     </row>
     <row r="729">
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>5534.74</v>
+        <v>5426.41</v>
       </c>
     </row>
     <row r="730">
@@ -44985,7 +44985,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>2554.84</v>
+        <v>2504.83</v>
       </c>
     </row>
     <row r="731">
@@ -45046,7 +45046,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>4427.79</v>
+        <v>4341.13</v>
       </c>
     </row>
     <row r="732">
@@ -45107,7 +45107,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>2767.37</v>
+        <v>2713.2</v>
       </c>
     </row>
     <row r="733">
@@ -45168,7 +45168,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>2374.6</v>
+        <v>2328.12</v>
       </c>
     </row>
     <row r="734">
@@ -45229,7 +45229,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>2379.94</v>
+        <v>2333.36</v>
       </c>
     </row>
     <row r="735">
@@ -45290,7 +45290,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>3320.85</v>
+        <v>3255.84</v>
       </c>
     </row>
     <row r="736">
@@ -45351,7 +45351,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>5534.74</v>
+        <v>5426.41</v>
       </c>
     </row>
     <row r="737">
@@ -45412,7 +45412,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>66416.92</v>
+        <v>65116.88</v>
       </c>
     </row>
     <row r="738">
@@ -45473,7 +45473,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>4664.96</v>
+        <v>4573.65</v>
       </c>
     </row>
     <row r="739">
@@ -45534,7 +45534,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>5534.74</v>
+        <v>5426.41</v>
       </c>
     </row>
     <row r="740">
@@ -45595,7 +45595,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>11069.49</v>
+        <v>10852.81</v>
       </c>
     </row>
     <row r="741">
@@ -45656,7 +45656,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>4427.79</v>
+        <v>4341.13</v>
       </c>
     </row>
     <row r="742">
@@ -45717,7 +45717,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>6641.69</v>
+        <v>6511.69</v>
       </c>
     </row>
     <row r="743">
@@ -45778,7 +45778,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>4427.79</v>
+        <v>4362.19</v>
       </c>
     </row>
     <row r="744">
@@ -45839,7 +45839,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>3320.85</v>
+        <v>3271.64</v>
       </c>
     </row>
     <row r="745">
@@ -45900,7 +45900,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>7195.17</v>
+        <v>7088.56</v>
       </c>
     </row>
     <row r="746">
@@ -45961,7 +45961,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>3320.85</v>
+        <v>3271.64</v>
       </c>
     </row>
     <row r="747">
@@ -46022,7 +46022,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>3320.85</v>
+        <v>3271.64</v>
       </c>
     </row>
     <row r="748">
@@ -46083,7 +46083,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>8302.110000000001</v>
+        <v>8179.11</v>
       </c>
     </row>
     <row r="749">
@@ -46144,7 +46144,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>3874.32</v>
+        <v>3816.92</v>
       </c>
     </row>
     <row r="750">
@@ -46205,7 +46205,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>33208.46</v>
+        <v>32716.45</v>
       </c>
     </row>
     <row r="751">
@@ -46266,7 +46266,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>2656.68</v>
+        <v>2617.32</v>
       </c>
     </row>
     <row r="752">
@@ -46327,7 +46327,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>2490.63</v>
+        <v>2453.73</v>
       </c>
     </row>
     <row r="753">
@@ -46388,7 +46388,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>4427.79</v>
+        <v>4362.19</v>
       </c>
     </row>
     <row r="754">
@@ -46449,7 +46449,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>3320.85</v>
+        <v>3271.64</v>
       </c>
     </row>
     <row r="755">
@@ -46510,7 +46510,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>5254.5</v>
+        <v>5176.65</v>
       </c>
     </row>
     <row r="756">
@@ -46571,7 +46571,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>4906.33</v>
+        <v>4833.64</v>
       </c>
     </row>
     <row r="757">
@@ -46632,7 +46632,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>23799.4</v>
+        <v>23446.79</v>
       </c>
     </row>
     <row r="758">
@@ -46693,7 +46693,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>3652.93</v>
+        <v>3598.81</v>
       </c>
     </row>
     <row r="759">
@@ -46754,7 +46754,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>23245.92</v>
+        <v>22901.51</v>
       </c>
     </row>
     <row r="760">
@@ -46815,7 +46815,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>6641.69</v>
+        <v>6543.29</v>
       </c>
     </row>
     <row r="761">
@@ -46876,7 +46876,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>2523.84</v>
+        <v>2486.45</v>
       </c>
     </row>
     <row r="762">
@@ -46937,7 +46937,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>22138.97</v>
+        <v>21810.96</v>
       </c>
     </row>
     <row r="763">
@@ -46998,7 +46998,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>6641.69</v>
+        <v>6543.29</v>
       </c>
     </row>
     <row r="764">
@@ -47059,7 +47059,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>2379.94</v>
+        <v>2344.68</v>
       </c>
     </row>
     <row r="765">
@@ -47120,7 +47120,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>3320.85</v>
+        <v>3271.64</v>
       </c>
     </row>
     <row r="766">
@@ -47181,7 +47181,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>5534.74</v>
+        <v>5452.74</v>
       </c>
     </row>
     <row r="767">
@@ -47242,7 +47242,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>2374.6</v>
+        <v>2339.42</v>
       </c>
     </row>
     <row r="768">
@@ -47368,7 +47368,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>5120.32</v>
+        <v>5044.46</v>
       </c>
     </row>
     <row r="770">
@@ -47429,7 +47429,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>7915.35</v>
+        <v>7798.07</v>
       </c>
     </row>
     <row r="771">
@@ -47490,7 +47490,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>3874.32</v>
+        <v>3816.92</v>
       </c>
     </row>
     <row r="772">
@@ -47551,7 +47551,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>12176.43</v>
+        <v>11996.03</v>
       </c>
     </row>
     <row r="773">
@@ -47612,7 +47612,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>4427.79</v>
+        <v>4362.19</v>
       </c>
     </row>
     <row r="774">
@@ -47673,7 +47673,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>4981.27</v>
+        <v>4907.47</v>
       </c>
     </row>
     <row r="775">
@@ -47734,7 +47734,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>33208.46</v>
+        <v>32716.45</v>
       </c>
     </row>
     <row r="776">
@@ -47795,7 +47795,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>9409.059999999999</v>
+        <v>9269.66</v>
       </c>
     </row>
     <row r="777">
@@ -47856,7 +47856,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>5601.16</v>
+        <v>5518.17</v>
       </c>
     </row>
     <row r="778">
@@ -47917,7 +47917,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>6758.18</v>
+        <v>6658.05</v>
       </c>
     </row>
     <row r="779">
@@ -47978,7 +47978,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>55347.43</v>
+        <v>54527.41</v>
       </c>
     </row>
     <row r="780">
@@ -48039,7 +48039,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>77486.39999999999</v>
+        <v>76338.38</v>
       </c>
     </row>
     <row r="781">
@@ -48100,7 +48100,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>4427.79</v>
+        <v>4362.19</v>
       </c>
     </row>
     <row r="782">
@@ -48161,7 +48161,7 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>3320.85</v>
+        <v>3271.64</v>
       </c>
     </row>
     <row r="783">
@@ -48222,7 +48222,7 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>7416.56</v>
+        <v>7306.67</v>
       </c>
     </row>
     <row r="784">
@@ -48283,7 +48283,7 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>5534.74</v>
+        <v>5452.74</v>
       </c>
     </row>
     <row r="785">
@@ -48344,7 +48344,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>7195.17</v>
+        <v>7088.56</v>
       </c>
     </row>
     <row r="786">
@@ -48405,7 +48405,7 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>22692.45</v>
+        <v>22356.24</v>
       </c>
     </row>
     <row r="787">
@@ -48466,7 +48466,7 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>16604.23</v>
+        <v>16358.22</v>
       </c>
     </row>
     <row r="788">
@@ -48527,7 +48527,7 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>2767.37</v>
+        <v>2726.37</v>
       </c>
     </row>
     <row r="789">
@@ -48588,7 +48588,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>8714.280000000001</v>
+        <v>8585.17</v>
       </c>
     </row>
     <row r="790">
@@ -48649,7 +48649,7 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>3892.19</v>
+        <v>3834.52</v>
       </c>
     </row>
     <row r="791">
@@ -48710,7 +48710,7 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>13836.86</v>
+        <v>13552.49</v>
       </c>
     </row>
     <row r="792">
@@ -48771,7 +48771,7 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>17711.18</v>
+        <v>17347.18</v>
       </c>
     </row>
     <row r="793">
@@ -48832,7 +48832,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>11018.82</v>
+        <v>10792.36</v>
       </c>
     </row>
     <row r="794">
@@ -48893,7 +48893,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>2379.94</v>
+        <v>2331.03</v>
       </c>
     </row>
     <row r="795">
@@ -48954,7 +48954,7 @@
         </is>
       </c>
       <c r="M795" s="2" t="n">
-        <v>11069.49</v>
+        <v>10841.99</v>
       </c>
     </row>
     <row r="796">
@@ -49015,7 +49015,7 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>22138.97</v>
+        <v>21683.98</v>
       </c>
     </row>
     <row r="797">
@@ -49076,7 +49076,7 @@
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>27740.35</v>
+        <v>27170.24</v>
       </c>
     </row>
     <row r="798">
@@ -49137,7 +49137,7 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>8855.59</v>
+        <v>8673.59</v>
       </c>
     </row>
     <row r="799">
@@ -49198,7 +49198,7 @@
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>7176.88</v>
+        <v>7029.38</v>
       </c>
     </row>
     <row r="800">
@@ -49259,7 +49259,7 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>3320.85</v>
+        <v>3252.6</v>
       </c>
     </row>
     <row r="801">
@@ -49320,7 +49320,7 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>11069.49</v>
+        <v>10841.99</v>
       </c>
     </row>
     <row r="802">
@@ -49381,7 +49381,7 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>13836.86</v>
+        <v>13552.49</v>
       </c>
     </row>
     <row r="803">
@@ -49442,7 +49442,7 @@
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>2668.34</v>
+        <v>2613.5</v>
       </c>
     </row>
     <row r="804">
@@ -49503,7 +49503,7 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>3155.39</v>
+        <v>3090.54</v>
       </c>
     </row>
     <row r="805">
@@ -49564,7 +49564,7 @@
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>5987.69</v>
+        <v>5864.63</v>
       </c>
     </row>
     <row r="806">
@@ -49625,7 +49625,7 @@
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>3274.42</v>
+        <v>3207.12</v>
       </c>
     </row>
     <row r="807">
@@ -49686,7 +49686,7 @@
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>7721.23</v>
+        <v>7562.55</v>
       </c>
     </row>
     <row r="808">
@@ -49747,7 +49747,7 @@
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>5534.74</v>
+        <v>5420.99</v>
       </c>
     </row>
     <row r="809">
@@ -49808,7 +49808,7 @@
         </is>
       </c>
       <c r="M809" s="2" t="n">
-        <v>16604.23</v>
+        <v>16262.98</v>
       </c>
     </row>
     <row r="810">
@@ -49869,7 +49869,7 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>2379.94</v>
+        <v>2331.03</v>
       </c>
     </row>
     <row r="811">
@@ -49930,7 +49930,7 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>2379.94</v>
+        <v>2331.03</v>
       </c>
     </row>
     <row r="812">
@@ -49991,7 +49991,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>19648.34</v>
+        <v>19244.53</v>
       </c>
     </row>
     <row r="813">
@@ -50052,7 +50052,7 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>11069.49</v>
+        <v>10841.99</v>
       </c>
     </row>
     <row r="814">
@@ -50113,7 +50113,7 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>13283.38</v>
+        <v>13010.39</v>
       </c>
     </row>
     <row r="815">
@@ -50174,7 +50174,7 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>2374.6</v>
+        <v>2325.8</v>
       </c>
     </row>
     <row r="816">
@@ -50235,7 +50235,7 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>2374.6</v>
+        <v>2325.8</v>
       </c>
     </row>
     <row r="817">
@@ -50296,7 +50296,7 @@
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>2545.98</v>
+        <v>2493.66</v>
       </c>
     </row>
     <row r="818">
@@ -50357,7 +50357,7 @@
         </is>
       </c>
       <c r="M818" s="2" t="n">
-        <v>35422.36</v>
+        <v>34694.36</v>
       </c>
     </row>
     <row r="819">
@@ -50418,7 +50418,7 @@
         </is>
       </c>
       <c r="M819" s="2" t="n">
-        <v>2391.01</v>
+        <v>2341.87</v>
       </c>
     </row>
     <row r="820">
@@ -50479,7 +50479,7 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>2379.35</v>
+        <v>2330.45</v>
       </c>
     </row>
     <row r="821">
@@ -50540,7 +50540,7 @@
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>5534.74</v>
+        <v>5420.99</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/suministro-de-combustibles/jun-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/jun-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24415,7 +24415,7 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
@@ -24465,7 +24465,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24587,7 +24587,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24770,7 +24770,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -25502,7 +25502,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25868,7 +25868,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -26051,7 +26051,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26234,7 +26234,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26417,7 +26417,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -28552,7 +28552,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28735,7 +28735,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28918,7 +28918,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29406,7 +29406,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29528,7 +29528,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29650,7 +29650,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29955,7 +29955,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30138,7 +30138,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30382,7 +30382,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30565,7 +30565,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30870,7 +30870,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -32151,7 +32151,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32212,7 +32212,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -33798,7 +33798,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33920,7 +33920,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -34347,7 +34347,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34713,7 +34713,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34896,7 +34896,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -35018,7 +35018,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35399,7 +35399,7 @@
       </c>
       <c r="K573" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L573" t="inlineStr">
@@ -35632,7 +35632,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35815,7 +35815,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -36364,7 +36364,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -37157,7 +37157,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37706,7 +37706,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -38316,7 +38316,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -39353,7 +39353,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39780,7 +39780,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39902,7 +39902,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -40146,7 +40146,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -40268,7 +40268,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40329,7 +40329,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40451,7 +40451,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40512,7 +40512,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40573,7 +40573,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40634,7 +40634,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40939,7 +40939,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -41671,7 +41671,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41915,7 +41915,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41976,7 +41976,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42037,7 +42037,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42159,7 +42159,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42220,7 +42220,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42769,7 +42769,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -42891,7 +42891,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -43074,7 +43074,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43806,7 +43806,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -44050,7 +44050,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -44477,7 +44477,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -44965,7 +44965,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -45270,7 +45270,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -46917,7 +46917,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -47039,7 +47039,7 @@
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
@@ -47298,7 +47298,7 @@
       </c>
       <c r="K768" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L768" t="inlineStr">
@@ -47531,7 +47531,7 @@
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
@@ -47775,7 +47775,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -48324,7 +48324,7 @@
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
@@ -48507,7 +48507,7 @@
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
@@ -48568,7 +48568,7 @@
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
@@ -48629,7 +48629,7 @@
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
@@ -49239,7 +49239,7 @@
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -49605,7 +49605,7 @@
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I806" t="inlineStr">
@@ -49666,7 +49666,7 @@
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I807" t="inlineStr">
@@ -49727,7 +49727,7 @@
       </c>
       <c r="H808" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I808" t="inlineStr">
@@ -50032,7 +50032,7 @@
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
